--- a/02_DIA_inicio_2026_analisis_assets/rbd_9629_escuela-basica-aliven_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9629_escuela-basica-aliven_nt2_rubricas.xlsx
@@ -1608,13 +1608,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E157F3C1-6C1D-4A89-B0DF-F0CAA5F3E9AC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3EDC6EB-0212-4A5A-85CA-ECFEC40A84B1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{248E00AA-BF67-4E3D-8944-278FAB498B94}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F9EF671-5B5E-4728-8C51-CCEE78F2C61E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54816019-4ADC-4F02-8752-F88C0E83C67A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D79A596C-6CAE-49EA-A0CD-90C68B27E170}"/>
 </file>